--- a/spreadsheet/chelsea_financial.xlsx
+++ b/spreadsheet/chelsea_financial.xlsx
@@ -410,10 +410,20 @@
       </c>
     </row>
     <row r="2" ht="12.75" customHeight="1" s="5">
-      <c r="A2" s="4" t="n"/>
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>7IM AAP Adventurous C Acc</t>
+        </is>
+      </c>
       <c r="B2" s="4" t="n"/>
-      <c r="C2" s="8" t="n"/>
-      <c r="D2" s="4" t="n"/>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>https://digital.feprecisionplus.com/Pdf/chelseafinancial/en-gb/chelsea/BFB9/O/?specialunittype=ORDN&amp;priipproductcode=17200457&amp;RangeCode=17200457</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="3" ht="12.75" customHeight="1" s="5">
       <c r="A3" s="4" t="n"/>
@@ -12116,6 +12126,9 @@
     </row>
     <row r="1048576" ht="12.75" customHeight="1" s="5"/>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
+  </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="1" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/spreadsheet/chelsea_financial.xlsx
+++ b/spreadsheet/chelsea_financial.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,6 +30,13 @@
       <b val="1"/>
       <color rgb="00000000"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color theme="10"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -55,15 +62,23 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -426,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -457,7 +472,769 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>7IM AAP Adventurous C Acc</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>https://digital.feprecisionplus.com/Pdf/chelseafinancial/en-gb/chelsea/BFB9/O/?specialunittype=ORDN&amp;priipproductcode=17200457&amp;RangeCode=17200457</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>7IM AAP Adventurous C Inc</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr"/>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>https://digital.feprecisionplus.com/Pdf/chelseafinancial/en-gb/chelsea/BFB8/O/?specialunittype=ORDN&amp;priipproductcode=17200457&amp;RangeCode=17200457</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Artemis Global Income I Acc</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr"/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>https://digital.feprecisionplus.com/Pdf/chelseafinancial/en-gb/chelsea/JXZ1/O/?specialunittype=ORDN&amp;priipproductcode=17200457&amp;RangeCode=17200457</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Artemis Global Income I Inc</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr"/>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>https://digital.feprecisionplus.com/Pdf/chelseafinancial/en-gb/chelsea/JXZ0/O/?specialunittype=ORDN&amp;priipproductcode=17200457&amp;RangeCode=17200457</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Baillie Gifford Emerging Markets Leading Companies B Dis GBP</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr"/>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>https://digital.feprecisionplus.com/Pdf/chelseafinancial/en-gb/chelsea/B460/O/?specialunittype=ORDN&amp;priipproductcode=17200457&amp;RangeCode=17200457</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Baillie Gifford European B Acc</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr"/>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>https://digital.feprecisionplus.com/Pdf/chelseafinancial/en-gb/chelsea/BG90/O/?specialunittype=ORDN&amp;priipproductcode=17200457&amp;RangeCode=17200457</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>BlackRock US Dynamic D Inc</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr"/>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>https://digital.feprecisionplus.com/Pdf/chelseafinancial/en-gb/chelsea/GTZY/O/?specialunittype=ORDN&amp;priipproductcode=17200457&amp;RangeCode=17200457</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>BlackRock US Mid-Cap Value D Acc</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr"/>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>https://digital.feprecisionplus.com/Pdf/chelseafinancial/en-gb/chelsea/GTZZ/O/?specialunittype=ORDN&amp;priipproductcode=17200457&amp;RangeCode=17200457</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>CT (Lux) Pan European Focus 3G Acc GBP</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr"/>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>https://digital.feprecisionplus.com/Pdf/chelseafinancial/en-gb/chelsea/KOTI/DC/?specialunittype=ORDN&amp;priipproductcode=17200457&amp;RangeCode=17200457</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>CT (Lux) UK Equities ZG GBP</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr"/>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>https://digital.feprecisionplus.com/Pdf/chelseafinancial/en-gb/chelsea/13C7/DC/?specialunittype=ORDN&amp;priipproductcode=17200457&amp;RangeCode=17200457</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>EdenTree Sustainable Global Equity B Dis GBP</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr"/>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>https://digital.feprecisionplus.com/Pdf/chelseafinancial/en-gb/chelsea/FR59/O/?specialunittype=ORDN&amp;priipproductcode=17200457&amp;RangeCode=17200457</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>EdenTree Sustainable Managed Income B Dis GBP</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr"/>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>https://digital.feprecisionplus.com/Pdf/chelseafinancial/en-gb/chelsea/A195/O/?specialunittype=ORDN&amp;priipproductcode=17200457&amp;RangeCode=17200457</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>First Sentier Global Listed Infrastructure B Inc GBP</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr"/>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>https://digital.feprecisionplus.com/Pdf/chelseafinancial/en-gb/chelsea/A6X4/O/?specialunittype=ORDN&amp;priipproductcode=17200457&amp;RangeCode=17200457</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>First Sentier Global Property Securities B Acc</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr"/>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>https://digital.feprecisionplus.com/Pdf/chelseafinancial/en-gb/chelsea/G999/O/?specialunittype=ORDN&amp;priipproductcode=17200457&amp;RangeCode=17200457</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>HSBC Balanced IC Inc</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr"/>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>https://digital.feprecisionplus.com/Pdf/chelseafinancial/en-gb/chelsea/JUZB/O/?specialunittype=ORDN&amp;priipproductcode=17200457&amp;RangeCode=17200457</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>HSBC Corporate Bond C Acc</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr"/>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>https://digital.feprecisionplus.com/Pdf/chelseafinancial/en-gb/chelsea/GTNE/O/?specialunittype=ORDN&amp;priipproductcode=17200457&amp;RangeCode=17200457</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>JPM JPM Diversified Growth C Acc</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr"/>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>https://digital.feprecisionplus.com/Pdf/chelseafinancial/en-gb/chelsea/I0KR/O/?specialunittype=ORDN&amp;priipproductcode=17200457&amp;RangeCode=17200457</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>JPM Japan C Inc</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr"/>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>https://digital.feprecisionplus.com/Pdf/chelseafinancial/en-gb/chelsea/0YDU/O/?specialunittype=ORDN&amp;priipproductcode=17200457&amp;RangeCode=17200457</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>L&amp;G Active Short Dated Sterling Corporate Bond I Dist</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr"/>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>https://digital.feprecisionplus.com/Pdf/chelseafinancial/en-gb/chelsea/GTPT/O/?specialunittype=ORDN&amp;priipproductcode=17200457&amp;RangeCode=17200457</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>L&amp;G Active Sterling Corporate Bond I Acc GBP</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr"/>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>https://digital.feprecisionplus.com/Pdf/chelseafinancial/en-gb/chelsea/LT88/O/?specialunittype=ORDN&amp;priipproductcode=17200457&amp;RangeCode=17200457</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Liontrust Balanced C Acc</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr"/>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>https://digital.feprecisionplus.com/Pdf/chelseafinancial/en-gb/chelsea/GQKV/O/?specialunittype=ORDN&amp;priipproductcode=17200457&amp;RangeCode=17200457</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Liontrust Balanced C Inc</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>https://digital.feprecisionplus.com/Pdf/chelseafinancial/en-gb/chelsea/GQKX/O/?specialunittype=ORDN&amp;priipproductcode=17200457&amp;RangeCode=17200457</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;G Global Emerging Markets I Acc GBP</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>https://digital.feprecisionplus.com/Pdf/chelseafinancial/en-gb/chelsea/EFP6/O/?specialunittype=ORDN&amp;priipproductcode=17200457&amp;RangeCode=17200457</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>M&amp;G Global Emerging Markets I Inc GBP</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>https://digital.feprecisionplus.com/Pdf/chelseafinancial/en-gb/chelsea/EFP7/O/?specialunittype=ORDN&amp;priipproductcode=17200457&amp;RangeCode=17200457</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>MI Verbatim Portfolio 3 B Acc</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>https://digital.feprecisionplus.com/Pdf/chelseafinancial/en-gb/chelsea/IBE8/O/?specialunittype=ORDN&amp;priipproductcode=17200457&amp;RangeCode=17200457</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>MI Verbatim Portfolio 4 B Acc</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>https://digital.feprecisionplus.com/Pdf/chelseafinancial/en-gb/chelsea/IBF0/O/?specialunittype=ORDN&amp;priipproductcode=17200457&amp;RangeCode=17200457</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Premier Miton Liberation VI C Acc GBP</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>https://digital.feprecisionplus.com/Pdf/chelseafinancial/en-gb/chelsea/LWE9/O/?specialunittype=ORDN&amp;priipproductcode=17200457&amp;RangeCode=17200457</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Premier Miton Liberation VII C Acc GBP</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>https://digital.feprecisionplus.com/Pdf/chelseafinancial/en-gb/chelsea/LWF1/O/?specialunittype=ORDN&amp;priipproductcode=17200457&amp;RangeCode=17200457</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Royal London Sustainable Diversified Trust C Inc</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>https://digital.feprecisionplus.com/Pdf/chelseafinancial/en-gb/chelsea/GVWE/O/?specialunittype=ORDN&amp;priipproductcode=17200457&amp;RangeCode=17200457</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Royal London Sustainable Leaders Trust C Acc</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>https://digital.feprecisionplus.com/Pdf/chelseafinancial/en-gb/chelsea/GVVX/O/?specialunittype=ORDN&amp;priipproductcode=17200457&amp;RangeCode=17200457</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Schroder Sustainable UK Equity Z Inc</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>https://digital.feprecisionplus.com/Pdf/chelseafinancial/en-gb/chelsea/KR45/O/?specialunittype=ORDN&amp;priipproductcode=17200457&amp;RangeCode=17200457</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Schroder Tokyo Z Acc</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>https://digital.feprecisionplus.com/Pdf/chelseafinancial/en-gb/chelsea/NND5/O/?specialunittype=ORDN&amp;priipproductcode=17200457&amp;RangeCode=17200457</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Thesis Stonehage Fleming International B Inc</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>https://digital.feprecisionplus.com/Pdf/chelseafinancial/en-gb/chelsea/C121/O/?specialunittype=ORDN&amp;priipproductcode=17200457&amp;RangeCode=17200457</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Thesis Stonehage Fleming International C Acc</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="3" t="inlineStr">
+        <is>
+          <t>https://digital.feprecisionplus.com/Pdf/chelseafinancial/en-gb/chelsea/J86T/O/?specialunittype=ORDN&amp;priipproductcode=17200457&amp;RangeCode=17200457</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Vanguard Global Equity A Acc</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>https://digital.feprecisionplus.com/Pdf/chelseafinancial/en-gb/chelsea/N01X/O/?specialunittype=ORDN&amp;priipproductcode=17200457&amp;RangeCode=17200457</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Vanguard Global Equity A Inc</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="3" t="inlineStr">
+        <is>
+          <t>https://digital.feprecisionplus.com/Pdf/chelseafinancial/en-gb/chelsea/N01W/O/?specialunittype=ORDN&amp;priipproductcode=17200457&amp;RangeCode=17200457</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>WS Keyridge Portfolio III C Inc</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>https://digital.feprecisionplus.com/Pdf/chelseafinancial/en-gb/chelsea/JL8R/O/?specialunittype=ORDN&amp;priipproductcode=17200457&amp;RangeCode=17200457</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>WS Keyridge Portfolio IV C Acc</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>https://digital.feprecisionplus.com/Pdf/chelseafinancial/en-gb/chelsea/JL9A/O/?specialunittype=ORDN&amp;priipproductcode=17200457&amp;RangeCode=17200457</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>iShares ESG Screened Overseas Corporate Bond Index (UK) D Acc</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>https://digital.feprecisionplus.com/Pdf/chelseafinancial/en-gb/chelsea/G6ID/O/?specialunittype=ORDN&amp;priipproductcode=17200457&amp;RangeCode=17200457</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>iShares ESG Screened Overseas Corporate Bond Index (UK) D Inc</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>https://digital.feprecisionplus.com/Pdf/chelseafinancial/en-gb/chelsea/KMWH/O/?specialunittype=ORDN&amp;priipproductcode=17200457&amp;RangeCode=17200457</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="C41" r:id="rId40"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>